--- a/02_加值成品/九下/九下4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下4-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-1 全球氣候變遷　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三下學期 九下4-1 全球氣候變遷　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>留住地表熱的氣體稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>溫室氣體</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>如CO₂</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>過量溫室氣體造成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>沿海低地</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>全球暖化</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>溫室氣體</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>暖化</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>主要溫室氣體是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>二氧化碳</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>暖化</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>CO₂</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>暖化造成海平面？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>維持適居溫度</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>沿海低地</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>融冰</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>減少排放的途徑稱？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>減緩</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>兩者並行</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>調適</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>減量</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>調整生活以適應變化稱？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>調適</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>維持適居溫度</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>燃燒化石燃料會排放？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>二氧化碳</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>更極端</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>兩者並行</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>沿海低地</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>排碳</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>發展再生能源屬於？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>減緩</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>沿海低地</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>減排</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>過多溫室氣體導致全球？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>減緩</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>溫室氣體</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>暖化</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>暖化</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>減少溫室氣體排放的途徑稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>減緩</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>暖化</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>減量</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-1 全球氣候變遷　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三下學期 九下4-1 全球氣候變遷　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>適度溫室效應的作用？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>維持適居溫度</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>溫室氣體</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>調適</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>必要</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>氣候變遷造成天氣？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>沿海低地</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>維持適居溫度</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>更極端</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>極端</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>防洪耐旱建設屬於？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>減緩</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>溫室氣體</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>調適</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>節能減碳屬於？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>調適</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>溫室氣體</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>減緩</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>減排</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>暖化對農業影響？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>作物與產量受衝擊</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>取代化石燃料減少CO₂排放</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>海面上升淹沒沿海改變生態</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>海平面上升極端降雨颱風增強</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>農業</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>海平面上升威脅？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>沿海低地</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>維持適居溫度</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>淹沒</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>搭乘大眾運輸有助？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>兩者並行</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>減少排碳</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>減緩</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>減緩與調適應如何？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>兩者並行</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>減緩</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>並重</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>全球暖化使海平面？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>沿海低地</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>上升</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>兩者並行</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>調適</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>融冰</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>調整生活與建設適應變化稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>調適</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>上升</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>全球暖化</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>適應</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三下學期 九下4-1 全球氣候變遷　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三下學期 九下4-1 全球氣候變遷　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明溫室效應如何造成全球暖化？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>海面上升淹沒沿海改變生態</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>減緩用再生能源、調適建防洪</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>溫室氣體增加留住更多熱能使均溫上升</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>比較減緩與調適的差別並各舉例？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>減緩治本較慢調適因應現有衝擊</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>節電少開車減少浪費</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>作物與產量受衝擊</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>對策</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>氣候變遷對臺灣可能的影響？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>減緩用再生能源、調適建防洪</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>留住更多熱能使均溫上升</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>取代化石燃料減少CO₂排放</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>海平面上升極端降雨颱風增強</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>在地</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>個人如何為減碳盡力？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>減緩治本較慢調適因應現有衝擊</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中聚焦暖化與對策</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>節電少開車減少浪費</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>作物與產量受衝擊</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>行動</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>為何減緩與調適需並行？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>減緩治本較慢調適因應現有衝擊</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>海面上升淹沒沿海改變生態</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>留住更多熱能使均溫上升</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>並行</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>冰川融化對全球的連鎖影響？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>取代化石燃料減少CO₂排放</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>作物與產量受衝擊</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>海面上升淹沒沿海改變生態</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>連鎖</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>再生能源如何幫助減緩暖化？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>留住更多熱能使均溫上升</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>作物與產量受衝擊</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>取代化石燃料減少CO₂排放</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>海面上升淹沒沿海改變生態</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>減排</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何國中不談臭氧洞聖嬰？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>溫室氣體增加留住更多熱能使均溫上升</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>減緩用再生能源、調適建防洪</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>移高中,國中聚焦暖化與對策</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>留住更多熱能使均溫上升</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>溫室效應過強為何造成暖化？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>減緩治本較慢調適因應現有衝擊</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>減緩用再生能源、調適建防洪</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>留住更多熱能使均溫上升</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>機制</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>減緩與調適各舉一例？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中聚焦暖化與對策</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>作物與產量受衝擊</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>減緩用再生能源、調適建防洪</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>對策</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九下/九下4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下4-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>如CO₂</t>
+          <t>如CO₂：這類氣體能把地表散發出的熱能留住，像二氧化碳就是常見的溫室氣體</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>暖化</t>
+          <t>暖化：空氣中溫室氣體太多，留住過多熱能，就會使地球整體溫度不斷上升</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>CO₂</t>
+          <t>CO₂：燃燒化石燃料排放出的二氧化碳，是造成溫室效應加劇最主要的氣體</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>融冰</t>
+          <t>融冰：全球暖化使高山與極地的冰融化、海水受熱膨脹，導致海平面逐漸上升</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>減量</t>
+          <t>減量：從源頭減少溫室氣體排放量、放慢暖化速度的做法，稱為減緩</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>適應：調整生活方式與各項建設，讓自己能適應已經發生的氣候變化，稱為調適</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>排碳</t>
+          <t>排碳：煤炭、石油等化石燃料燃燒時，會釋放出大量的二氧化碳到空氣中</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>減排</t>
+          <t>減排：太陽能、風力等再生能源能取代化石燃料，減少碳排放，屬於減緩暖化的做法</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>暖化</t>
+          <t>暖化：大氣中溫室氣體(如二氧化碳)增加,會使地球留住更多熱量,造成全球平均氣溫上升</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>減量</t>
+          <t>減量：直接想辦法降低溫室氣體排放量、減緩暖化速度的做法稱為減緩</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>必要</t>
+          <t>必要：適當程度的溫室效應能讓地球保有溫暖的氣溫，是生物能夠生存的重要條件</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>極端</t>
+          <t>極端：氣候變遷會讓天氣型態變得更劇烈，例如更強的豪雨、更長的乾旱與熱浪</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>適應：興建防洪設施、培育耐旱作物等，都是幫助人類適應氣候變化的調適做法</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>減排</t>
+          <t>減排：日常生活中節省能源、減少碳排放的行為，屬於減緩暖化的具體做法</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>農業</t>
+          <t>農業：氣溫與降雨型態改變會影響農作物的生長，導致產量與品質受到衝擊</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>淹沒</t>
+          <t>淹沒：海平面持續上升會威脅到地勢較低的沿海地區，增加淹水甚至被淹沒的風險</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>減緩</t>
+          <t>減緩：多人共乘大眾運輸工具能減少私人汽機車的使用，降低二氧化碳的排放量</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>並重</t>
+          <t>並重：既要努力減少排放放慢暖化(減緩)，也要同時調整生活因應已發生的變化(調適)，兩者缺一不可</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>融冰</t>
+          <t>融冰：全球暖化使極地冰川和冰帽大量融化,加上海水受熱膨脹,共同導致海平面上升</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>適應</t>
+          <t>適應：面對已經發生的氣候變化,調整生活方式與建設(如防洪設施)來因應,這種做法稱為調適</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：空氣中溫室氣體濃度增加，會讓地表散發的熱能更不容易散失到太空，留住的熱越來越多，導致全球平均氣溫上升</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>對策</t>
+          <t>對策：減緩是從源頭減少溫室氣體排放，例如發展再生能源；調適則是調整作法去因應已經發生的變化，例如興建防洪設施</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>在地</t>
+          <t>在地：氣候變遷可能使臺灣沿海面臨海平面上升的威脅，也可能出現更極端的暴雨和更強烈的颱風</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>行動</t>
+          <t>行動：日常生活中隨手節約用電、盡量搭乘大眾運輸取代開車，並減少不必要的資源浪費，都是個人能做的減碳行動</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>並行</t>
+          <t>並行：減緩暖化的效果需要長時間才能顯現，屬於治本；而調適能立即因應目前已經發生的氣候衝擊，所以兩者必須同時進行</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>連鎖</t>
+          <t>連鎖：冰川大量融化會使海平面上升，淹沒地勢低窪的沿海地區，也會改變當地原本的生態環境</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>減排</t>
+          <t>減排：太陽能、風力等再生能源發電時不需要燃燒化石燃料，能有效取代並減少二氧化碳的排放量</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：臭氧洞和聖嬰現象等進階主題留到高中再深入學習，國中階段聚焦在全球暖化的成因與因應對策</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>機制</t>
+          <t>機制：溫室氣體會吸收並留住原本要散失到太空的熱能,當溫室氣體濃度過高,留住的熱能過多,就會使地球平均氣溫持續上升</t>
         </is>
       </c>
     </row>
@@ -1870,37 +1870,37 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>減緩與調適各舉一例？</t>
+          <t>減緩與調適各舉一例說明差異？</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>移高中,國中聚焦暖化與對策</t>
+          <t>海平面上升極端降雨颱風增強</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>作物與產量受衝擊</t>
+          <t>溫室氣體增加留住更多熱能使均溫上升</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
+          <t>留住更多熱能使均溫上升</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
           <t>減緩用再生能源、調適建防洪</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
-        </is>
-      </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>對策</t>
+          <t>對策：減緩是從源頭減少溫室氣體排放,例如改用再生能源發電;調適是接受氣候已經改變,採取行動因應後果,例如興建防洪堤,兩者角度不同</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九下/九下4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九下/九下4-1_三種難度測驗卷.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>沿海低地</t>
+          <t>更極端</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
+          <t>減少排碳</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>溫室氣體</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>二氧化碳</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>二氧化碳</t>
+          <t>上升</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>溫室氣體</t>
+          <t>兩者並行</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1515,17 +1515,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>海面上升淹沒沿海改變生態</t>
+          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>減緩用再生能源、調適建防洪</t>
+          <t>海平面上升極端降雨颱風增強</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
+          <t>取代化石燃料減少CO₂排放</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>減緩治本較慢調適因應現有衝擊</t>
+          <t>取代化石燃料減少CO₂排放</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>減緩用再生能源、調適建防洪</t>
+          <t>海面上升淹沒沿海改變生態</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>減緩減少排放(再生能源);調適適應變化(防洪)</t>
+          <t>作物與產量受衝擊</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
